--- a/cosatcal/CosatCal_dati.xlsx
+++ b/cosatcal/CosatCal_dati.xlsx
@@ -10,19 +10,17 @@
     <sheet name="Parametri" sheetId="2" r:id="rId2"/>
     <sheet name="Materiali" sheetId="3" r:id="rId3"/>
     <sheet name="Ferro" sheetId="4" r:id="rId4"/>
-    <sheet name="Pepito" sheetId="5" r:id="rId5"/>
-    <sheet name="Ottone" sheetId="6" r:id="rId6"/>
-    <sheet name="Inox" sheetId="7" r:id="rId7"/>
-    <sheet name="Inox P" sheetId="8" r:id="rId8"/>
-    <sheet name="Alluminio" sheetId="9" r:id="rId9"/>
-    <sheet name="Zincato" sheetId="10" r:id="rId10"/>
+    <sheet name="Inox" sheetId="5" r:id="rId5"/>
+    <sheet name="Inox P" sheetId="6" r:id="rId6"/>
+    <sheet name="Alluminio" sheetId="7" r:id="rId7"/>
+    <sheet name="Zincato" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="53">
   <si>
     <t>Base dati CosatCal</t>
   </si>
@@ -156,12 +154,6 @@
     <t>Alluminio</t>
   </si>
   <si>
-    <t>Ottone</t>
-  </si>
-  <si>
-    <t>Pepito</t>
-  </si>
-  <si>
     <t>spessore_mm</t>
   </si>
   <si>
@@ -178,12 +170,6 @@
   </si>
   <si>
     <t>DD11</t>
-  </si>
-  <si>
-    <t>aaaa</t>
-  </si>
-  <si>
-    <t>DCDD</t>
   </si>
   <si>
     <t>14301</t>
@@ -561,1901 +547,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D300"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="14.00390625" customWidth="1"/>
-    <col min="2" max="3" width="12.00390625" customWidth="1"/>
-    <col min="4" max="4" width="18.00390625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" s="4">
-        <v>6.28</v>
-      </c>
-      <c r="D2" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" s="4">
-        <v>7.85</v>
-      </c>
-      <c r="D3" s="4">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="4">
-        <v>9.42</v>
-      </c>
-      <c r="D4" s="4">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" s="4">
-        <v>11.8</v>
-      </c>
-      <c r="D5" s="4">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4">
-        <v>2</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="4">
-        <v>15.7</v>
-      </c>
-      <c r="D6" s="4">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4">
-        <v>2.5</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="4">
-        <v>19.6</v>
-      </c>
-      <c r="D7" s="4">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4">
-        <v>3</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" s="4">
-        <v>23.6</v>
-      </c>
-      <c r="D8" s="4">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="4"/>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="4"/>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="4"/>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="4"/>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="4"/>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="4"/>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="4"/>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="4"/>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="4"/>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="4"/>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="4"/>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="4"/>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="4"/>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="4"/>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="4"/>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="4"/>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="4"/>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="4"/>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="4"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="4"/>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="4"/>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="4"/>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="4"/>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="4"/>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="4"/>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="4"/>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="4"/>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="4"/>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="4"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="4"/>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="4"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="4"/>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="4"/>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="4"/>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="4"/>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="4"/>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="4"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="4"/>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="4"/>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="4"/>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="4"/>
-      <c r="B81" s="4"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="4"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="4"/>
-      <c r="B82" s="4"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="4"/>
-      <c r="B83" s="4"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="4"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="4"/>
-      <c r="B84" s="4"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="4"/>
-      <c r="B85" s="4"/>
-      <c r="C85" s="4"/>
-      <c r="D85" s="4"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="4"/>
-      <c r="B86" s="4"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="4"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="4"/>
-      <c r="B87" s="4"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="4"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="4"/>
-      <c r="B88" s="4"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="4"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="4"/>
-      <c r="B89" s="4"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="4"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="4"/>
-      <c r="B90" s="4"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="4"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="4"/>
-      <c r="B91" s="4"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="4"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="4"/>
-      <c r="B92" s="4"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="4"/>
-      <c r="B93" s="4"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="4"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="4"/>
-      <c r="B94" s="4"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="4"/>
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="4"/>
-      <c r="B96" s="4"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="4"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="4"/>
-      <c r="B97" s="4"/>
-      <c r="C97" s="4"/>
-      <c r="D97" s="4"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="4"/>
-      <c r="B98" s="4"/>
-      <c r="C98" s="4"/>
-      <c r="D98" s="4"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="4"/>
-      <c r="B99" s="4"/>
-      <c r="C99" s="4"/>
-      <c r="D99" s="4"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="4"/>
-      <c r="B100" s="4"/>
-      <c r="C100" s="4"/>
-      <c r="D100" s="4"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="4"/>
-      <c r="B101" s="4"/>
-      <c r="C101" s="4"/>
-      <c r="D101" s="4"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="4"/>
-      <c r="B102" s="4"/>
-      <c r="C102" s="4"/>
-      <c r="D102" s="4"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="4"/>
-      <c r="B103" s="4"/>
-      <c r="C103" s="4"/>
-      <c r="D103" s="4"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="4"/>
-      <c r="B104" s="4"/>
-      <c r="C104" s="4"/>
-      <c r="D104" s="4"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="4"/>
-      <c r="B105" s="4"/>
-      <c r="C105" s="4"/>
-      <c r="D105" s="4"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="4"/>
-      <c r="B106" s="4"/>
-      <c r="C106" s="4"/>
-      <c r="D106" s="4"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="4"/>
-      <c r="B107" s="4"/>
-      <c r="C107" s="4"/>
-      <c r="D107" s="4"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="4"/>
-      <c r="B108" s="4"/>
-      <c r="C108" s="4"/>
-      <c r="D108" s="4"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="4"/>
-      <c r="B109" s="4"/>
-      <c r="C109" s="4"/>
-      <c r="D109" s="4"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="4"/>
-      <c r="B110" s="4"/>
-      <c r="C110" s="4"/>
-      <c r="D110" s="4"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="4"/>
-      <c r="B111" s="4"/>
-      <c r="C111" s="4"/>
-      <c r="D111" s="4"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="4"/>
-      <c r="B112" s="4"/>
-      <c r="C112" s="4"/>
-      <c r="D112" s="4"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="4"/>
-      <c r="B113" s="4"/>
-      <c r="C113" s="4"/>
-      <c r="D113" s="4"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="4"/>
-      <c r="B114" s="4"/>
-      <c r="C114" s="4"/>
-      <c r="D114" s="4"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="4"/>
-      <c r="B115" s="4"/>
-      <c r="C115" s="4"/>
-      <c r="D115" s="4"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="4"/>
-      <c r="B116" s="4"/>
-      <c r="C116" s="4"/>
-      <c r="D116" s="4"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="4"/>
-      <c r="B117" s="4"/>
-      <c r="C117" s="4"/>
-      <c r="D117" s="4"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="4"/>
-      <c r="B118" s="4"/>
-      <c r="C118" s="4"/>
-      <c r="D118" s="4"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="4"/>
-      <c r="B119" s="4"/>
-      <c r="C119" s="4"/>
-      <c r="D119" s="4"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="4"/>
-      <c r="B120" s="4"/>
-      <c r="C120" s="4"/>
-      <c r="D120" s="4"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="4"/>
-      <c r="B121" s="4"/>
-      <c r="C121" s="4"/>
-      <c r="D121" s="4"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="4"/>
-      <c r="B122" s="4"/>
-      <c r="C122" s="4"/>
-      <c r="D122" s="4"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="4"/>
-      <c r="B123" s="4"/>
-      <c r="C123" s="4"/>
-      <c r="D123" s="4"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="4"/>
-      <c r="B124" s="4"/>
-      <c r="C124" s="4"/>
-      <c r="D124" s="4"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="4"/>
-      <c r="B125" s="4"/>
-      <c r="C125" s="4"/>
-      <c r="D125" s="4"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="4"/>
-      <c r="B126" s="4"/>
-      <c r="C126" s="4"/>
-      <c r="D126" s="4"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="4"/>
-      <c r="B127" s="4"/>
-      <c r="C127" s="4"/>
-      <c r="D127" s="4"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="4"/>
-      <c r="B128" s="4"/>
-      <c r="C128" s="4"/>
-      <c r="D128" s="4"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="4"/>
-      <c r="B129" s="4"/>
-      <c r="C129" s="4"/>
-      <c r="D129" s="4"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="4"/>
-      <c r="B130" s="4"/>
-      <c r="C130" s="4"/>
-      <c r="D130" s="4"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="4"/>
-      <c r="B131" s="4"/>
-      <c r="C131" s="4"/>
-      <c r="D131" s="4"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="4"/>
-      <c r="B132" s="4"/>
-      <c r="C132" s="4"/>
-      <c r="D132" s="4"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="4"/>
-      <c r="B133" s="4"/>
-      <c r="C133" s="4"/>
-      <c r="D133" s="4"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="4"/>
-      <c r="B134" s="4"/>
-      <c r="C134" s="4"/>
-      <c r="D134" s="4"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="4"/>
-      <c r="B135" s="4"/>
-      <c r="C135" s="4"/>
-      <c r="D135" s="4"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="4"/>
-      <c r="B136" s="4"/>
-      <c r="C136" s="4"/>
-      <c r="D136" s="4"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="4"/>
-      <c r="B137" s="4"/>
-      <c r="C137" s="4"/>
-      <c r="D137" s="4"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="4"/>
-      <c r="B138" s="4"/>
-      <c r="C138" s="4"/>
-      <c r="D138" s="4"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="4"/>
-      <c r="B139" s="4"/>
-      <c r="C139" s="4"/>
-      <c r="D139" s="4"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="4"/>
-      <c r="B140" s="4"/>
-      <c r="C140" s="4"/>
-      <c r="D140" s="4"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="4"/>
-      <c r="B141" s="4"/>
-      <c r="C141" s="4"/>
-      <c r="D141" s="4"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="4"/>
-      <c r="B142" s="4"/>
-      <c r="C142" s="4"/>
-      <c r="D142" s="4"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="4"/>
-      <c r="B143" s="4"/>
-      <c r="C143" s="4"/>
-      <c r="D143" s="4"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="4"/>
-      <c r="B144" s="4"/>
-      <c r="C144" s="4"/>
-      <c r="D144" s="4"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="4"/>
-      <c r="B145" s="4"/>
-      <c r="C145" s="4"/>
-      <c r="D145" s="4"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="4"/>
-      <c r="B146" s="4"/>
-      <c r="C146" s="4"/>
-      <c r="D146" s="4"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="4"/>
-      <c r="B147" s="4"/>
-      <c r="C147" s="4"/>
-      <c r="D147" s="4"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="4"/>
-      <c r="B148" s="4"/>
-      <c r="C148" s="4"/>
-      <c r="D148" s="4"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="4"/>
-      <c r="B149" s="4"/>
-      <c r="C149" s="4"/>
-      <c r="D149" s="4"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="4"/>
-      <c r="B150" s="4"/>
-      <c r="C150" s="4"/>
-      <c r="D150" s="4"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="4"/>
-      <c r="B151" s="4"/>
-      <c r="C151" s="4"/>
-      <c r="D151" s="4"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="4"/>
-      <c r="B152" s="4"/>
-      <c r="C152" s="4"/>
-      <c r="D152" s="4"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="4"/>
-      <c r="B153" s="4"/>
-      <c r="C153" s="4"/>
-      <c r="D153" s="4"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="4"/>
-      <c r="B154" s="4"/>
-      <c r="C154" s="4"/>
-      <c r="D154" s="4"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="4"/>
-      <c r="B155" s="4"/>
-      <c r="C155" s="4"/>
-      <c r="D155" s="4"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="4"/>
-      <c r="B156" s="4"/>
-      <c r="C156" s="4"/>
-      <c r="D156" s="4"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="4"/>
-      <c r="B157" s="4"/>
-      <c r="C157" s="4"/>
-      <c r="D157" s="4"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="4"/>
-      <c r="B158" s="4"/>
-      <c r="C158" s="4"/>
-      <c r="D158" s="4"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="4"/>
-      <c r="B159" s="4"/>
-      <c r="C159" s="4"/>
-      <c r="D159" s="4"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="4"/>
-      <c r="B160" s="4"/>
-      <c r="C160" s="4"/>
-      <c r="D160" s="4"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="4"/>
-      <c r="B161" s="4"/>
-      <c r="C161" s="4"/>
-      <c r="D161" s="4"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="4"/>
-      <c r="B162" s="4"/>
-      <c r="C162" s="4"/>
-      <c r="D162" s="4"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="4"/>
-      <c r="B163" s="4"/>
-      <c r="C163" s="4"/>
-      <c r="D163" s="4"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="4"/>
-      <c r="B164" s="4"/>
-      <c r="C164" s="4"/>
-      <c r="D164" s="4"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="4"/>
-      <c r="B165" s="4"/>
-      <c r="C165" s="4"/>
-      <c r="D165" s="4"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="4"/>
-      <c r="B166" s="4"/>
-      <c r="C166" s="4"/>
-      <c r="D166" s="4"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="4"/>
-      <c r="B167" s="4"/>
-      <c r="C167" s="4"/>
-      <c r="D167" s="4"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="4"/>
-      <c r="B168" s="4"/>
-      <c r="C168" s="4"/>
-      <c r="D168" s="4"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="4"/>
-      <c r="B169" s="4"/>
-      <c r="C169" s="4"/>
-      <c r="D169" s="4"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="4"/>
-      <c r="B170" s="4"/>
-      <c r="C170" s="4"/>
-      <c r="D170" s="4"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="4"/>
-      <c r="B171" s="4"/>
-      <c r="C171" s="4"/>
-      <c r="D171" s="4"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="4"/>
-      <c r="B172" s="4"/>
-      <c r="C172" s="4"/>
-      <c r="D172" s="4"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="4"/>
-      <c r="B173" s="4"/>
-      <c r="C173" s="4"/>
-      <c r="D173" s="4"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="4"/>
-      <c r="B174" s="4"/>
-      <c r="C174" s="4"/>
-      <c r="D174" s="4"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="4"/>
-      <c r="B175" s="4"/>
-      <c r="C175" s="4"/>
-      <c r="D175" s="4"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="4"/>
-      <c r="B176" s="4"/>
-      <c r="C176" s="4"/>
-      <c r="D176" s="4"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="4"/>
-      <c r="B177" s="4"/>
-      <c r="C177" s="4"/>
-      <c r="D177" s="4"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="4"/>
-      <c r="B178" s="4"/>
-      <c r="C178" s="4"/>
-      <c r="D178" s="4"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="4"/>
-      <c r="B179" s="4"/>
-      <c r="C179" s="4"/>
-      <c r="D179" s="4"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="4"/>
-      <c r="B180" s="4"/>
-      <c r="C180" s="4"/>
-      <c r="D180" s="4"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="4"/>
-      <c r="B181" s="4"/>
-      <c r="C181" s="4"/>
-      <c r="D181" s="4"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="4"/>
-      <c r="B182" s="4"/>
-      <c r="C182" s="4"/>
-      <c r="D182" s="4"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="4"/>
-      <c r="B183" s="4"/>
-      <c r="C183" s="4"/>
-      <c r="D183" s="4"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="4"/>
-      <c r="B184" s="4"/>
-      <c r="C184" s="4"/>
-      <c r="D184" s="4"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="4"/>
-      <c r="B185" s="4"/>
-      <c r="C185" s="4"/>
-      <c r="D185" s="4"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="4"/>
-      <c r="B186" s="4"/>
-      <c r="C186" s="4"/>
-      <c r="D186" s="4"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="4"/>
-      <c r="B187" s="4"/>
-      <c r="C187" s="4"/>
-      <c r="D187" s="4"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="4"/>
-      <c r="B188" s="4"/>
-      <c r="C188" s="4"/>
-      <c r="D188" s="4"/>
-    </row>
-    <row r="189">
-      <c r="A189" s="4"/>
-      <c r="B189" s="4"/>
-      <c r="C189" s="4"/>
-      <c r="D189" s="4"/>
-    </row>
-    <row r="190">
-      <c r="A190" s="4"/>
-      <c r="B190" s="4"/>
-      <c r="C190" s="4"/>
-      <c r="D190" s="4"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="4"/>
-      <c r="B191" s="4"/>
-      <c r="C191" s="4"/>
-      <c r="D191" s="4"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="4"/>
-      <c r="B192" s="4"/>
-      <c r="C192" s="4"/>
-      <c r="D192" s="4"/>
-    </row>
-    <row r="193">
-      <c r="A193" s="4"/>
-      <c r="B193" s="4"/>
-      <c r="C193" s="4"/>
-      <c r="D193" s="4"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="4"/>
-      <c r="B194" s="4"/>
-      <c r="C194" s="4"/>
-      <c r="D194" s="4"/>
-    </row>
-    <row r="195">
-      <c r="A195" s="4"/>
-      <c r="B195" s="4"/>
-      <c r="C195" s="4"/>
-      <c r="D195" s="4"/>
-    </row>
-    <row r="196">
-      <c r="A196" s="4"/>
-      <c r="B196" s="4"/>
-      <c r="C196" s="4"/>
-      <c r="D196" s="4"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="4"/>
-      <c r="B197" s="4"/>
-      <c r="C197" s="4"/>
-      <c r="D197" s="4"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="4"/>
-      <c r="B198" s="4"/>
-      <c r="C198" s="4"/>
-      <c r="D198" s="4"/>
-    </row>
-    <row r="199">
-      <c r="A199" s="4"/>
-      <c r="B199" s="4"/>
-      <c r="C199" s="4"/>
-      <c r="D199" s="4"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="4"/>
-      <c r="B200" s="4"/>
-      <c r="C200" s="4"/>
-      <c r="D200" s="4"/>
-    </row>
-    <row r="201">
-      <c r="A201" s="4"/>
-      <c r="B201" s="4"/>
-      <c r="C201" s="4"/>
-      <c r="D201" s="4"/>
-    </row>
-    <row r="202">
-      <c r="A202" s="4"/>
-      <c r="B202" s="4"/>
-      <c r="C202" s="4"/>
-      <c r="D202" s="4"/>
-    </row>
-    <row r="203">
-      <c r="A203" s="4"/>
-      <c r="B203" s="4"/>
-      <c r="C203" s="4"/>
-      <c r="D203" s="4"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="4"/>
-      <c r="B204" s="4"/>
-      <c r="C204" s="4"/>
-      <c r="D204" s="4"/>
-    </row>
-    <row r="205">
-      <c r="A205" s="4"/>
-      <c r="B205" s="4"/>
-      <c r="C205" s="4"/>
-      <c r="D205" s="4"/>
-    </row>
-    <row r="206">
-      <c r="A206" s="4"/>
-      <c r="B206" s="4"/>
-      <c r="C206" s="4"/>
-      <c r="D206" s="4"/>
-    </row>
-    <row r="207">
-      <c r="A207" s="4"/>
-      <c r="B207" s="4"/>
-      <c r="C207" s="4"/>
-      <c r="D207" s="4"/>
-    </row>
-    <row r="208">
-      <c r="A208" s="4"/>
-      <c r="B208" s="4"/>
-      <c r="C208" s="4"/>
-      <c r="D208" s="4"/>
-    </row>
-    <row r="209">
-      <c r="A209" s="4"/>
-      <c r="B209" s="4"/>
-      <c r="C209" s="4"/>
-      <c r="D209" s="4"/>
-    </row>
-    <row r="210">
-      <c r="A210" s="4"/>
-      <c r="B210" s="4"/>
-      <c r="C210" s="4"/>
-      <c r="D210" s="4"/>
-    </row>
-    <row r="211">
-      <c r="A211" s="4"/>
-      <c r="B211" s="4"/>
-      <c r="C211" s="4"/>
-      <c r="D211" s="4"/>
-    </row>
-    <row r="212">
-      <c r="A212" s="4"/>
-      <c r="B212" s="4"/>
-      <c r="C212" s="4"/>
-      <c r="D212" s="4"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="4"/>
-      <c r="B213" s="4"/>
-      <c r="C213" s="4"/>
-      <c r="D213" s="4"/>
-    </row>
-    <row r="214">
-      <c r="A214" s="4"/>
-      <c r="B214" s="4"/>
-      <c r="C214" s="4"/>
-      <c r="D214" s="4"/>
-    </row>
-    <row r="215">
-      <c r="A215" s="4"/>
-      <c r="B215" s="4"/>
-      <c r="C215" s="4"/>
-      <c r="D215" s="4"/>
-    </row>
-    <row r="216">
-      <c r="A216" s="4"/>
-      <c r="B216" s="4"/>
-      <c r="C216" s="4"/>
-      <c r="D216" s="4"/>
-    </row>
-    <row r="217">
-      <c r="A217" s="4"/>
-      <c r="B217" s="4"/>
-      <c r="C217" s="4"/>
-      <c r="D217" s="4"/>
-    </row>
-    <row r="218">
-      <c r="A218" s="4"/>
-      <c r="B218" s="4"/>
-      <c r="C218" s="4"/>
-      <c r="D218" s="4"/>
-    </row>
-    <row r="219">
-      <c r="A219" s="4"/>
-      <c r="B219" s="4"/>
-      <c r="C219" s="4"/>
-      <c r="D219" s="4"/>
-    </row>
-    <row r="220">
-      <c r="A220" s="4"/>
-      <c r="B220" s="4"/>
-      <c r="C220" s="4"/>
-      <c r="D220" s="4"/>
-    </row>
-    <row r="221">
-      <c r="A221" s="4"/>
-      <c r="B221" s="4"/>
-      <c r="C221" s="4"/>
-      <c r="D221" s="4"/>
-    </row>
-    <row r="222">
-      <c r="A222" s="4"/>
-      <c r="B222" s="4"/>
-      <c r="C222" s="4"/>
-      <c r="D222" s="4"/>
-    </row>
-    <row r="223">
-      <c r="A223" s="4"/>
-      <c r="B223" s="4"/>
-      <c r="C223" s="4"/>
-      <c r="D223" s="4"/>
-    </row>
-    <row r="224">
-      <c r="A224" s="4"/>
-      <c r="B224" s="4"/>
-      <c r="C224" s="4"/>
-      <c r="D224" s="4"/>
-    </row>
-    <row r="225">
-      <c r="A225" s="4"/>
-      <c r="B225" s="4"/>
-      <c r="C225" s="4"/>
-      <c r="D225" s="4"/>
-    </row>
-    <row r="226">
-      <c r="A226" s="4"/>
-      <c r="B226" s="4"/>
-      <c r="C226" s="4"/>
-      <c r="D226" s="4"/>
-    </row>
-    <row r="227">
-      <c r="A227" s="4"/>
-      <c r="B227" s="4"/>
-      <c r="C227" s="4"/>
-      <c r="D227" s="4"/>
-    </row>
-    <row r="228">
-      <c r="A228" s="4"/>
-      <c r="B228" s="4"/>
-      <c r="C228" s="4"/>
-      <c r="D228" s="4"/>
-    </row>
-    <row r="229">
-      <c r="A229" s="4"/>
-      <c r="B229" s="4"/>
-      <c r="C229" s="4"/>
-      <c r="D229" s="4"/>
-    </row>
-    <row r="230">
-      <c r="A230" s="4"/>
-      <c r="B230" s="4"/>
-      <c r="C230" s="4"/>
-      <c r="D230" s="4"/>
-    </row>
-    <row r="231">
-      <c r="A231" s="4"/>
-      <c r="B231" s="4"/>
-      <c r="C231" s="4"/>
-      <c r="D231" s="4"/>
-    </row>
-    <row r="232">
-      <c r="A232" s="4"/>
-      <c r="B232" s="4"/>
-      <c r="C232" s="4"/>
-      <c r="D232" s="4"/>
-    </row>
-    <row r="233">
-      <c r="A233" s="4"/>
-      <c r="B233" s="4"/>
-      <c r="C233" s="4"/>
-      <c r="D233" s="4"/>
-    </row>
-    <row r="234">
-      <c r="A234" s="4"/>
-      <c r="B234" s="4"/>
-      <c r="C234" s="4"/>
-      <c r="D234" s="4"/>
-    </row>
-    <row r="235">
-      <c r="A235" s="4"/>
-      <c r="B235" s="4"/>
-      <c r="C235" s="4"/>
-      <c r="D235" s="4"/>
-    </row>
-    <row r="236">
-      <c r="A236" s="4"/>
-      <c r="B236" s="4"/>
-      <c r="C236" s="4"/>
-      <c r="D236" s="4"/>
-    </row>
-    <row r="237">
-      <c r="A237" s="4"/>
-      <c r="B237" s="4"/>
-      <c r="C237" s="4"/>
-      <c r="D237" s="4"/>
-    </row>
-    <row r="238">
-      <c r="A238" s="4"/>
-      <c r="B238" s="4"/>
-      <c r="C238" s="4"/>
-      <c r="D238" s="4"/>
-    </row>
-    <row r="239">
-      <c r="A239" s="4"/>
-      <c r="B239" s="4"/>
-      <c r="C239" s="4"/>
-      <c r="D239" s="4"/>
-    </row>
-    <row r="240">
-      <c r="A240" s="4"/>
-      <c r="B240" s="4"/>
-      <c r="C240" s="4"/>
-      <c r="D240" s="4"/>
-    </row>
-    <row r="241">
-      <c r="A241" s="4"/>
-      <c r="B241" s="4"/>
-      <c r="C241" s="4"/>
-      <c r="D241" s="4"/>
-    </row>
-    <row r="242">
-      <c r="A242" s="4"/>
-      <c r="B242" s="4"/>
-      <c r="C242" s="4"/>
-      <c r="D242" s="4"/>
-    </row>
-    <row r="243">
-      <c r="A243" s="4"/>
-      <c r="B243" s="4"/>
-      <c r="C243" s="4"/>
-      <c r="D243" s="4"/>
-    </row>
-    <row r="244">
-      <c r="A244" s="4"/>
-      <c r="B244" s="4"/>
-      <c r="C244" s="4"/>
-      <c r="D244" s="4"/>
-    </row>
-    <row r="245">
-      <c r="A245" s="4"/>
-      <c r="B245" s="4"/>
-      <c r="C245" s="4"/>
-      <c r="D245" s="4"/>
-    </row>
-    <row r="246">
-      <c r="A246" s="4"/>
-      <c r="B246" s="4"/>
-      <c r="C246" s="4"/>
-      <c r="D246" s="4"/>
-    </row>
-    <row r="247">
-      <c r="A247" s="4"/>
-      <c r="B247" s="4"/>
-      <c r="C247" s="4"/>
-      <c r="D247" s="4"/>
-    </row>
-    <row r="248">
-      <c r="A248" s="4"/>
-      <c r="B248" s="4"/>
-      <c r="C248" s="4"/>
-      <c r="D248" s="4"/>
-    </row>
-    <row r="249">
-      <c r="A249" s="4"/>
-      <c r="B249" s="4"/>
-      <c r="C249" s="4"/>
-      <c r="D249" s="4"/>
-    </row>
-    <row r="250">
-      <c r="A250" s="4"/>
-      <c r="B250" s="4"/>
-      <c r="C250" s="4"/>
-      <c r="D250" s="4"/>
-    </row>
-    <row r="251">
-      <c r="A251" s="4"/>
-      <c r="B251" s="4"/>
-      <c r="C251" s="4"/>
-      <c r="D251" s="4"/>
-    </row>
-    <row r="252">
-      <c r="A252" s="4"/>
-      <c r="B252" s="4"/>
-      <c r="C252" s="4"/>
-      <c r="D252" s="4"/>
-    </row>
-    <row r="253">
-      <c r="A253" s="4"/>
-      <c r="B253" s="4"/>
-      <c r="C253" s="4"/>
-      <c r="D253" s="4"/>
-    </row>
-    <row r="254">
-      <c r="A254" s="4"/>
-      <c r="B254" s="4"/>
-      <c r="C254" s="4"/>
-      <c r="D254" s="4"/>
-    </row>
-    <row r="255">
-      <c r="A255" s="4"/>
-      <c r="B255" s="4"/>
-      <c r="C255" s="4"/>
-      <c r="D255" s="4"/>
-    </row>
-    <row r="256">
-      <c r="A256" s="4"/>
-      <c r="B256" s="4"/>
-      <c r="C256" s="4"/>
-      <c r="D256" s="4"/>
-    </row>
-    <row r="257">
-      <c r="A257" s="4"/>
-      <c r="B257" s="4"/>
-      <c r="C257" s="4"/>
-      <c r="D257" s="4"/>
-    </row>
-    <row r="258">
-      <c r="A258" s="4"/>
-      <c r="B258" s="4"/>
-      <c r="C258" s="4"/>
-      <c r="D258" s="4"/>
-    </row>
-    <row r="259">
-      <c r="A259" s="4"/>
-      <c r="B259" s="4"/>
-      <c r="C259" s="4"/>
-      <c r="D259" s="4"/>
-    </row>
-    <row r="260">
-      <c r="A260" s="4"/>
-      <c r="B260" s="4"/>
-      <c r="C260" s="4"/>
-      <c r="D260" s="4"/>
-    </row>
-    <row r="261">
-      <c r="A261" s="4"/>
-      <c r="B261" s="4"/>
-      <c r="C261" s="4"/>
-      <c r="D261" s="4"/>
-    </row>
-    <row r="262">
-      <c r="A262" s="4"/>
-      <c r="B262" s="4"/>
-      <c r="C262" s="4"/>
-      <c r="D262" s="4"/>
-    </row>
-    <row r="263">
-      <c r="A263" s="4"/>
-      <c r="B263" s="4"/>
-      <c r="C263" s="4"/>
-      <c r="D263" s="4"/>
-    </row>
-    <row r="264">
-      <c r="A264" s="4"/>
-      <c r="B264" s="4"/>
-      <c r="C264" s="4"/>
-      <c r="D264" s="4"/>
-    </row>
-    <row r="265">
-      <c r="A265" s="4"/>
-      <c r="B265" s="4"/>
-      <c r="C265" s="4"/>
-      <c r="D265" s="4"/>
-    </row>
-    <row r="266">
-      <c r="A266" s="4"/>
-      <c r="B266" s="4"/>
-      <c r="C266" s="4"/>
-      <c r="D266" s="4"/>
-    </row>
-    <row r="267">
-      <c r="A267" s="4"/>
-      <c r="B267" s="4"/>
-      <c r="C267" s="4"/>
-      <c r="D267" s="4"/>
-    </row>
-    <row r="268">
-      <c r="A268" s="4"/>
-      <c r="B268" s="4"/>
-      <c r="C268" s="4"/>
-      <c r="D268" s="4"/>
-    </row>
-    <row r="269">
-      <c r="A269" s="4"/>
-      <c r="B269" s="4"/>
-      <c r="C269" s="4"/>
-      <c r="D269" s="4"/>
-    </row>
-    <row r="270">
-      <c r="A270" s="4"/>
-      <c r="B270" s="4"/>
-      <c r="C270" s="4"/>
-      <c r="D270" s="4"/>
-    </row>
-    <row r="271">
-      <c r="A271" s="4"/>
-      <c r="B271" s="4"/>
-      <c r="C271" s="4"/>
-      <c r="D271" s="4"/>
-    </row>
-    <row r="272">
-      <c r="A272" s="4"/>
-      <c r="B272" s="4"/>
-      <c r="C272" s="4"/>
-      <c r="D272" s="4"/>
-    </row>
-    <row r="273">
-      <c r="A273" s="4"/>
-      <c r="B273" s="4"/>
-      <c r="C273" s="4"/>
-      <c r="D273" s="4"/>
-    </row>
-    <row r="274">
-      <c r="A274" s="4"/>
-      <c r="B274" s="4"/>
-      <c r="C274" s="4"/>
-      <c r="D274" s="4"/>
-    </row>
-    <row r="275">
-      <c r="A275" s="4"/>
-      <c r="B275" s="4"/>
-      <c r="C275" s="4"/>
-      <c r="D275" s="4"/>
-    </row>
-    <row r="276">
-      <c r="A276" s="4"/>
-      <c r="B276" s="4"/>
-      <c r="C276" s="4"/>
-      <c r="D276" s="4"/>
-    </row>
-    <row r="277">
-      <c r="A277" s="4"/>
-      <c r="B277" s="4"/>
-      <c r="C277" s="4"/>
-      <c r="D277" s="4"/>
-    </row>
-    <row r="278">
-      <c r="A278" s="4"/>
-      <c r="B278" s="4"/>
-      <c r="C278" s="4"/>
-      <c r="D278" s="4"/>
-    </row>
-    <row r="279">
-      <c r="A279" s="4"/>
-      <c r="B279" s="4"/>
-      <c r="C279" s="4"/>
-      <c r="D279" s="4"/>
-    </row>
-    <row r="280">
-      <c r="A280" s="4"/>
-      <c r="B280" s="4"/>
-      <c r="C280" s="4"/>
-      <c r="D280" s="4"/>
-    </row>
-    <row r="281">
-      <c r="A281" s="4"/>
-      <c r="B281" s="4"/>
-      <c r="C281" s="4"/>
-      <c r="D281" s="4"/>
-    </row>
-    <row r="282">
-      <c r="A282" s="4"/>
-      <c r="B282" s="4"/>
-      <c r="C282" s="4"/>
-      <c r="D282" s="4"/>
-    </row>
-    <row r="283">
-      <c r="A283" s="4"/>
-      <c r="B283" s="4"/>
-      <c r="C283" s="4"/>
-      <c r="D283" s="4"/>
-    </row>
-    <row r="284">
-      <c r="A284" s="4"/>
-      <c r="B284" s="4"/>
-      <c r="C284" s="4"/>
-      <c r="D284" s="4"/>
-    </row>
-    <row r="285">
-      <c r="A285" s="4"/>
-      <c r="B285" s="4"/>
-      <c r="C285" s="4"/>
-      <c r="D285" s="4"/>
-    </row>
-    <row r="286">
-      <c r="A286" s="4"/>
-      <c r="B286" s="4"/>
-      <c r="C286" s="4"/>
-      <c r="D286" s="4"/>
-    </row>
-    <row r="287">
-      <c r="A287" s="4"/>
-      <c r="B287" s="4"/>
-      <c r="C287" s="4"/>
-      <c r="D287" s="4"/>
-    </row>
-    <row r="288">
-      <c r="A288" s="4"/>
-      <c r="B288" s="4"/>
-      <c r="C288" s="4"/>
-      <c r="D288" s="4"/>
-    </row>
-    <row r="289">
-      <c r="A289" s="4"/>
-      <c r="B289" s="4"/>
-      <c r="C289" s="4"/>
-      <c r="D289" s="4"/>
-    </row>
-    <row r="290">
-      <c r="A290" s="4"/>
-      <c r="B290" s="4"/>
-      <c r="C290" s="4"/>
-      <c r="D290" s="4"/>
-    </row>
-    <row r="291">
-      <c r="A291" s="4"/>
-      <c r="B291" s="4"/>
-      <c r="C291" s="4"/>
-      <c r="D291" s="4"/>
-    </row>
-    <row r="292">
-      <c r="A292" s="4"/>
-      <c r="B292" s="4"/>
-      <c r="C292" s="4"/>
-      <c r="D292" s="4"/>
-    </row>
-    <row r="293">
-      <c r="A293" s="4"/>
-      <c r="B293" s="4"/>
-      <c r="C293" s="4"/>
-      <c r="D293" s="4"/>
-    </row>
-    <row r="294">
-      <c r="A294" s="4"/>
-      <c r="B294" s="4"/>
-      <c r="C294" s="4"/>
-      <c r="D294" s="4"/>
-    </row>
-    <row r="295">
-      <c r="A295" s="4"/>
-      <c r="B295" s="4"/>
-      <c r="C295" s="4"/>
-      <c r="D295" s="4"/>
-    </row>
-    <row r="296">
-      <c r="A296" s="4"/>
-      <c r="B296" s="4"/>
-      <c r="C296" s="4"/>
-      <c r="D296" s="4"/>
-    </row>
-    <row r="297">
-      <c r="A297" s="4"/>
-      <c r="B297" s="4"/>
-      <c r="C297" s="4"/>
-      <c r="D297" s="4"/>
-    </row>
-    <row r="298">
-      <c r="A298" s="4"/>
-      <c r="B298" s="4"/>
-      <c r="C298" s="4"/>
-      <c r="D298" s="4"/>
-    </row>
-    <row r="299">
-      <c r="A299" s="4"/>
-      <c r="B299" s="4"/>
-      <c r="C299" s="4"/>
-      <c r="D299" s="4"/>
-    </row>
-    <row r="300">
-      <c r="A300" s="4"/>
-      <c r="B300" s="4"/>
-      <c r="C300" s="4"/>
-      <c r="D300" s="4"/>
-    </row>
-  </sheetData>
-  <dataValidations count="3">
-    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" errorTitle="Valore non valido" error="Spessore in mm (numero, es. 1.5)." sqref="A2:A300">
-      <formula1>0.1</formula1>
-      <formula2>60</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Valore non valido" error="Peso in kg/m² (&gt; 0)." sqref="C2:C300">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Valore non valido" error="Consumo in m³/h (&gt; 0)." sqref="D2:D300">
-      <formula1>0</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D300"/>
@@ -4339,7 +2430,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B300"/>
+  <dimension ref="A1:B298"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.00390625" customWidth="1"/>
@@ -4395,20 +2486,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="4">
-        <v>9</v>
-      </c>
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B8" s="4">
-        <v>2</v>
-      </c>
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
     </row>
     <row r="9">
       <c r="A9" s="4"/>
@@ -5570,17 +3653,9 @@
       <c r="A298" s="4"/>
       <c r="B298" s="4"/>
     </row>
-    <row r="299">
-      <c r="A299" s="4"/>
-      <c r="B299" s="4"/>
-    </row>
-    <row r="300">
-      <c r="A300" s="4"/>
-      <c r="B300" s="4"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Valore non valido" error="Inserire un prezzo &gt;= 0 (€/kg)." sqref="B2:B300">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Valore non valido" error="Inserire un prezzo &gt;= 0 (€/kg)." sqref="B2:B298">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -5604,16 +3679,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2">
@@ -5621,7 +3696,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C2" s="4">
         <v>6.28</v>
@@ -5635,7 +3710,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C3" s="4">
         <v>7.85</v>
@@ -5649,7 +3724,7 @@
         <v>1.2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C4" s="4">
         <v>9.42</v>
@@ -5663,7 +3738,7 @@
         <v>1.5</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C5" s="4">
         <v>11.8</v>
@@ -5677,7 +3752,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C6" s="4">
         <v>15.7</v>
@@ -5691,7 +3766,7 @@
         <v>2.5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C7" s="4">
         <v>19.6</v>
@@ -5705,7 +3780,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C8" s="4">
         <v>23.6</v>
@@ -5719,7 +3794,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C9" s="4">
         <v>31.4</v>
@@ -5733,7 +3808,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C10" s="4">
         <v>39.25</v>
@@ -5747,7 +3822,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C11" s="4">
         <v>47.1</v>
@@ -5761,7 +3836,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C12" s="4">
         <v>62.8</v>
@@ -5775,7 +3850,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C13" s="4">
         <v>78.5</v>
@@ -5789,7 +3864,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C14" s="4">
         <v>94.2</v>
@@ -7542,29 +5617,30 @@
   <cols>
     <col min="1" max="1" width="14.00390625" customWidth="1"/>
     <col min="2" max="2" width="12.00390625" customWidth="1"/>
-    <col min="3" max="4" width="18.00390625" customWidth="1"/>
+    <col min="3" max="3" width="17.8515625" customWidth="1"/>
+    <col min="4" max="4" width="18.00390625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4">
-        <v>23</v>
+        <v>0.8</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C2" s="4">
         <v>6.28</v>
@@ -7578,168 +5654,144 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C3" s="4">
         <v>7.85</v>
       </c>
       <c r="D3" s="4">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4">
-        <v>20</v>
+        <v>1.2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C4" s="4">
         <v>9.42</v>
       </c>
       <c r="D4" s="4">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4">
-        <v>24</v>
+        <v>1.5</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C5" s="4">
         <v>11.8</v>
       </c>
       <c r="D5" s="4">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C6" s="4">
         <v>15.7</v>
       </c>
       <c r="D6" s="4">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C7" s="4">
         <v>19.6</v>
       </c>
       <c r="D7" s="4">
-        <v>4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C8" s="4">
         <v>23.6</v>
       </c>
       <c r="D8" s="4">
-        <v>4</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C9" s="4">
         <v>31.4</v>
       </c>
       <c r="D9" s="4">
-        <v>1.5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C10" s="4">
         <v>39.25</v>
       </c>
       <c r="D10" s="4">
-        <v>44</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C11" s="4">
         <v>47.1</v>
       </c>
       <c r="D11" s="4">
-        <v>1.5</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4">
-        <v>2</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="4">
-        <v>62.8</v>
-      </c>
-      <c r="D12" s="4">
-        <v>34</v>
-      </c>
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
     </row>
     <row r="13">
-      <c r="A13" s="4">
-        <v>1</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="4">
-        <v>78.5</v>
-      </c>
-      <c r="D13" s="4">
-        <v>3</v>
-      </c>
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
     </row>
     <row r="14">
-      <c r="A14" s="4">
-        <v>1</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" s="4">
-        <v>31</v>
-      </c>
-      <c r="D14" s="4">
-        <v>2</v>
-      </c>
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
     </row>
     <row r="15">
       <c r="A15" s="4"/>
@@ -9472,6 +7524,9 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -9481,22 +7536,22 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.00390625" customWidth="1"/>
-    <col min="2" max="2" width="12.00390625" customWidth="1"/>
-    <col min="3" max="4" width="18.00390625" customWidth="1"/>
+    <col min="2" max="3" width="12.00390625" customWidth="1"/>
+    <col min="4" max="4" width="18.00390625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2">
@@ -9504,13 +7559,13 @@
         <v>0.8</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C2" s="4">
         <v>6.28</v>
       </c>
       <c r="D2" s="4">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -9518,13 +7573,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C3" s="4">
         <v>7.85</v>
       </c>
       <c r="D3" s="4">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -9532,13 +7587,13 @@
         <v>1.2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C4" s="4">
         <v>9.42</v>
       </c>
       <c r="D4" s="4">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -9546,13 +7601,13 @@
         <v>1.5</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C5" s="4">
-        <v>123</v>
+        <v>11.8</v>
       </c>
       <c r="D5" s="4">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -9560,13 +7615,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C6" s="4">
         <v>15.7</v>
       </c>
       <c r="D6" s="4">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -9574,13 +7629,13 @@
         <v>2.5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C7" s="4">
-        <v>19.623</v>
+        <v>19.6</v>
       </c>
       <c r="D7" s="4">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
@@ -9588,13 +7643,13 @@
         <v>3</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C8" s="4">
         <v>23.6</v>
       </c>
       <c r="D8" s="4">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
@@ -9602,84 +7657,44 @@
         <v>4</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C9" s="4">
-        <v>12</v>
+        <v>31.4</v>
       </c>
       <c r="D9" s="4">
-        <v>1.5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4">
-        <v>5</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" s="4">
-        <v>39.25</v>
-      </c>
-      <c r="D10" s="4">
-        <v>1.5</v>
-      </c>
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
     </row>
     <row r="11">
-      <c r="A11" s="4">
-        <v>6</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="4">
-        <v>47.1</v>
-      </c>
-      <c r="D11" s="4">
-        <v>1.5</v>
-      </c>
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
     </row>
     <row r="12">
-      <c r="A12" s="4">
-        <v>8</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="4">
-        <v>123</v>
-      </c>
-      <c r="D12" s="4">
-        <v>1.5</v>
-      </c>
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
     </row>
     <row r="13">
-      <c r="A13" s="4">
-        <v>10</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="4">
-        <v>78.5</v>
-      </c>
-      <c r="D13" s="4">
-        <v>1.5</v>
-      </c>
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
     </row>
     <row r="14">
-      <c r="A14" s="4">
-        <v>12</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="4">
-        <v>94.2</v>
-      </c>
-      <c r="D14" s="4">
-        <v>1.5</v>
-      </c>
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
     </row>
     <row r="15">
       <c r="A15" s="4"/>
@@ -11412,6 +9427,9 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -11422,22 +9440,22 @@
   <cols>
     <col min="1" max="1" width="14.00390625" customWidth="1"/>
     <col min="2" max="2" width="12.00390625" customWidth="1"/>
-    <col min="3" max="3" width="17.8515625" customWidth="1"/>
+    <col min="3" max="3" width="13.57421875" customWidth="1"/>
     <col min="4" max="4" width="18.00390625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2">
@@ -11445,13 +9463,13 @@
         <v>0.8</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C2" s="4">
-        <v>6.28</v>
+        <v>2.16</v>
       </c>
       <c r="D2" s="4">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -11459,13 +9477,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C3" s="4">
-        <v>7.85</v>
+        <v>2.7</v>
       </c>
       <c r="D3" s="4">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -11473,10 +9491,10 @@
         <v>1.2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C4" s="4">
-        <v>9.42</v>
+        <v>3.24</v>
       </c>
       <c r="D4" s="4">
         <v>24</v>
@@ -11487,10 +9505,10 @@
         <v>1.5</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C5" s="4">
-        <v>11.8</v>
+        <v>4.05</v>
       </c>
       <c r="D5" s="4">
         <v>24</v>
@@ -11501,13 +9519,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C6" s="4">
-        <v>15.7</v>
+        <v>5.4</v>
       </c>
       <c r="D6" s="4">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -11515,13 +9533,13 @@
         <v>2.5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C7" s="4">
-        <v>19.6</v>
+        <v>6.75</v>
       </c>
       <c r="D7" s="4">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -11529,13 +9547,13 @@
         <v>3</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C8" s="4">
-        <v>23.6</v>
+        <v>8.1</v>
       </c>
       <c r="D8" s="4">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
@@ -11543,13 +9561,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C9" s="4">
-        <v>31.4</v>
+        <v>10.8</v>
       </c>
       <c r="D9" s="4">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10">
@@ -11557,13 +9575,13 @@
         <v>5</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C10" s="4">
-        <v>39.25</v>
+        <v>13.5</v>
       </c>
       <c r="D10" s="4">
-        <v>67</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
@@ -11571,20 +9589,24 @@
         <v>6</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" s="4">
-        <v>47.1</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="C11" s="4"/>
       <c r="D11" s="4">
         <v>72</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
+      <c r="A12" s="4">
+        <v>8</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>51</v>
+      </c>
       <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
+      <c r="D12" s="4">
+        <v>72</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4"/>
@@ -13347,16 +11369,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2">
@@ -13364,13 +11386,13 @@
         <v>0.8</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C2" s="4">
         <v>6.28</v>
       </c>
       <c r="D2" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -13378,7 +11400,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C3" s="4">
         <v>7.85</v>
@@ -13392,7 +11414,7 @@
         <v>1.2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C4" s="4">
         <v>9.42</v>
@@ -13406,7 +11428,7 @@
         <v>1.5</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C5" s="4">
         <v>11.8</v>
@@ -13420,7 +11442,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C6" s="4">
         <v>15.7</v>
@@ -13434,13 +11456,13 @@
         <v>2.5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C7" s="4">
         <v>19.6</v>
       </c>
       <c r="D7" s="4">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
@@ -13448,28 +11470,20 @@
         <v>3</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C8" s="4">
         <v>23.6</v>
       </c>
       <c r="D8" s="4">
-        <v>35</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4">
-        <v>4</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="4">
-        <v>31.4</v>
-      </c>
-      <c r="D9" s="4">
-        <v>40</v>
-      </c>
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
     </row>
     <row r="10">
       <c r="A10" s="4"/>
@@ -13488,1930 +11502,6 @@
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="4"/>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="4"/>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="4"/>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="4"/>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="4"/>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="4"/>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="4"/>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="4"/>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="4"/>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="4"/>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="4"/>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="4"/>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="4"/>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="4"/>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="4"/>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="4"/>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="4"/>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="4"/>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="4"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="4"/>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="4"/>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="4"/>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="4"/>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="4"/>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="4"/>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="4"/>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="4"/>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="4"/>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="4"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="4"/>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="4"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="4"/>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="4"/>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="4"/>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="4"/>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="4"/>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="4"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="4"/>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="4"/>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="4"/>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="4"/>
-      <c r="B81" s="4"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="4"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="4"/>
-      <c r="B82" s="4"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="4"/>
-      <c r="B83" s="4"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="4"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="4"/>
-      <c r="B84" s="4"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="4"/>
-      <c r="B85" s="4"/>
-      <c r="C85" s="4"/>
-      <c r="D85" s="4"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="4"/>
-      <c r="B86" s="4"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="4"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="4"/>
-      <c r="B87" s="4"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="4"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="4"/>
-      <c r="B88" s="4"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="4"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="4"/>
-      <c r="B89" s="4"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="4"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="4"/>
-      <c r="B90" s="4"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="4"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="4"/>
-      <c r="B91" s="4"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="4"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="4"/>
-      <c r="B92" s="4"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="4"/>
-      <c r="B93" s="4"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="4"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="4"/>
-      <c r="B94" s="4"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="4"/>
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="4"/>
-      <c r="B96" s="4"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="4"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="4"/>
-      <c r="B97" s="4"/>
-      <c r="C97" s="4"/>
-      <c r="D97" s="4"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="4"/>
-      <c r="B98" s="4"/>
-      <c r="C98" s="4"/>
-      <c r="D98" s="4"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="4"/>
-      <c r="B99" s="4"/>
-      <c r="C99" s="4"/>
-      <c r="D99" s="4"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="4"/>
-      <c r="B100" s="4"/>
-      <c r="C100" s="4"/>
-      <c r="D100" s="4"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="4"/>
-      <c r="B101" s="4"/>
-      <c r="C101" s="4"/>
-      <c r="D101" s="4"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="4"/>
-      <c r="B102" s="4"/>
-      <c r="C102" s="4"/>
-      <c r="D102" s="4"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="4"/>
-      <c r="B103" s="4"/>
-      <c r="C103" s="4"/>
-      <c r="D103" s="4"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="4"/>
-      <c r="B104" s="4"/>
-      <c r="C104" s="4"/>
-      <c r="D104" s="4"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="4"/>
-      <c r="B105" s="4"/>
-      <c r="C105" s="4"/>
-      <c r="D105" s="4"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="4"/>
-      <c r="B106" s="4"/>
-      <c r="C106" s="4"/>
-      <c r="D106" s="4"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="4"/>
-      <c r="B107" s="4"/>
-      <c r="C107" s="4"/>
-      <c r="D107" s="4"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="4"/>
-      <c r="B108" s="4"/>
-      <c r="C108" s="4"/>
-      <c r="D108" s="4"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="4"/>
-      <c r="B109" s="4"/>
-      <c r="C109" s="4"/>
-      <c r="D109" s="4"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="4"/>
-      <c r="B110" s="4"/>
-      <c r="C110" s="4"/>
-      <c r="D110" s="4"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="4"/>
-      <c r="B111" s="4"/>
-      <c r="C111" s="4"/>
-      <c r="D111" s="4"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="4"/>
-      <c r="B112" s="4"/>
-      <c r="C112" s="4"/>
-      <c r="D112" s="4"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="4"/>
-      <c r="B113" s="4"/>
-      <c r="C113" s="4"/>
-      <c r="D113" s="4"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="4"/>
-      <c r="B114" s="4"/>
-      <c r="C114" s="4"/>
-      <c r="D114" s="4"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="4"/>
-      <c r="B115" s="4"/>
-      <c r="C115" s="4"/>
-      <c r="D115" s="4"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="4"/>
-      <c r="B116" s="4"/>
-      <c r="C116" s="4"/>
-      <c r="D116" s="4"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="4"/>
-      <c r="B117" s="4"/>
-      <c r="C117" s="4"/>
-      <c r="D117" s="4"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="4"/>
-      <c r="B118" s="4"/>
-      <c r="C118" s="4"/>
-      <c r="D118" s="4"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="4"/>
-      <c r="B119" s="4"/>
-      <c r="C119" s="4"/>
-      <c r="D119" s="4"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="4"/>
-      <c r="B120" s="4"/>
-      <c r="C120" s="4"/>
-      <c r="D120" s="4"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="4"/>
-      <c r="B121" s="4"/>
-      <c r="C121" s="4"/>
-      <c r="D121" s="4"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="4"/>
-      <c r="B122" s="4"/>
-      <c r="C122" s="4"/>
-      <c r="D122" s="4"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="4"/>
-      <c r="B123" s="4"/>
-      <c r="C123" s="4"/>
-      <c r="D123" s="4"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="4"/>
-      <c r="B124" s="4"/>
-      <c r="C124" s="4"/>
-      <c r="D124" s="4"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="4"/>
-      <c r="B125" s="4"/>
-      <c r="C125" s="4"/>
-      <c r="D125" s="4"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="4"/>
-      <c r="B126" s="4"/>
-      <c r="C126" s="4"/>
-      <c r="D126" s="4"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="4"/>
-      <c r="B127" s="4"/>
-      <c r="C127" s="4"/>
-      <c r="D127" s="4"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="4"/>
-      <c r="B128" s="4"/>
-      <c r="C128" s="4"/>
-      <c r="D128" s="4"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="4"/>
-      <c r="B129" s="4"/>
-      <c r="C129" s="4"/>
-      <c r="D129" s="4"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="4"/>
-      <c r="B130" s="4"/>
-      <c r="C130" s="4"/>
-      <c r="D130" s="4"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="4"/>
-      <c r="B131" s="4"/>
-      <c r="C131" s="4"/>
-      <c r="D131" s="4"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="4"/>
-      <c r="B132" s="4"/>
-      <c r="C132" s="4"/>
-      <c r="D132" s="4"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="4"/>
-      <c r="B133" s="4"/>
-      <c r="C133" s="4"/>
-      <c r="D133" s="4"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="4"/>
-      <c r="B134" s="4"/>
-      <c r="C134" s="4"/>
-      <c r="D134" s="4"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="4"/>
-      <c r="B135" s="4"/>
-      <c r="C135" s="4"/>
-      <c r="D135" s="4"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="4"/>
-      <c r="B136" s="4"/>
-      <c r="C136" s="4"/>
-      <c r="D136" s="4"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="4"/>
-      <c r="B137" s="4"/>
-      <c r="C137" s="4"/>
-      <c r="D137" s="4"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="4"/>
-      <c r="B138" s="4"/>
-      <c r="C138" s="4"/>
-      <c r="D138" s="4"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="4"/>
-      <c r="B139" s="4"/>
-      <c r="C139" s="4"/>
-      <c r="D139" s="4"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="4"/>
-      <c r="B140" s="4"/>
-      <c r="C140" s="4"/>
-      <c r="D140" s="4"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="4"/>
-      <c r="B141" s="4"/>
-      <c r="C141" s="4"/>
-      <c r="D141" s="4"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="4"/>
-      <c r="B142" s="4"/>
-      <c r="C142" s="4"/>
-      <c r="D142" s="4"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="4"/>
-      <c r="B143" s="4"/>
-      <c r="C143" s="4"/>
-      <c r="D143" s="4"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="4"/>
-      <c r="B144" s="4"/>
-      <c r="C144" s="4"/>
-      <c r="D144" s="4"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="4"/>
-      <c r="B145" s="4"/>
-      <c r="C145" s="4"/>
-      <c r="D145" s="4"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="4"/>
-      <c r="B146" s="4"/>
-      <c r="C146" s="4"/>
-      <c r="D146" s="4"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="4"/>
-      <c r="B147" s="4"/>
-      <c r="C147" s="4"/>
-      <c r="D147" s="4"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="4"/>
-      <c r="B148" s="4"/>
-      <c r="C148" s="4"/>
-      <c r="D148" s="4"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="4"/>
-      <c r="B149" s="4"/>
-      <c r="C149" s="4"/>
-      <c r="D149" s="4"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="4"/>
-      <c r="B150" s="4"/>
-      <c r="C150" s="4"/>
-      <c r="D150" s="4"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="4"/>
-      <c r="B151" s="4"/>
-      <c r="C151" s="4"/>
-      <c r="D151" s="4"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="4"/>
-      <c r="B152" s="4"/>
-      <c r="C152" s="4"/>
-      <c r="D152" s="4"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="4"/>
-      <c r="B153" s="4"/>
-      <c r="C153" s="4"/>
-      <c r="D153" s="4"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="4"/>
-      <c r="B154" s="4"/>
-      <c r="C154" s="4"/>
-      <c r="D154" s="4"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="4"/>
-      <c r="B155" s="4"/>
-      <c r="C155" s="4"/>
-      <c r="D155" s="4"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="4"/>
-      <c r="B156" s="4"/>
-      <c r="C156" s="4"/>
-      <c r="D156" s="4"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="4"/>
-      <c r="B157" s="4"/>
-      <c r="C157" s="4"/>
-      <c r="D157" s="4"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="4"/>
-      <c r="B158" s="4"/>
-      <c r="C158" s="4"/>
-      <c r="D158" s="4"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="4"/>
-      <c r="B159" s="4"/>
-      <c r="C159" s="4"/>
-      <c r="D159" s="4"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="4"/>
-      <c r="B160" s="4"/>
-      <c r="C160" s="4"/>
-      <c r="D160" s="4"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="4"/>
-      <c r="B161" s="4"/>
-      <c r="C161" s="4"/>
-      <c r="D161" s="4"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="4"/>
-      <c r="B162" s="4"/>
-      <c r="C162" s="4"/>
-      <c r="D162" s="4"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="4"/>
-      <c r="B163" s="4"/>
-      <c r="C163" s="4"/>
-      <c r="D163" s="4"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="4"/>
-      <c r="B164" s="4"/>
-      <c r="C164" s="4"/>
-      <c r="D164" s="4"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="4"/>
-      <c r="B165" s="4"/>
-      <c r="C165" s="4"/>
-      <c r="D165" s="4"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="4"/>
-      <c r="B166" s="4"/>
-      <c r="C166" s="4"/>
-      <c r="D166" s="4"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="4"/>
-      <c r="B167" s="4"/>
-      <c r="C167" s="4"/>
-      <c r="D167" s="4"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="4"/>
-      <c r="B168" s="4"/>
-      <c r="C168" s="4"/>
-      <c r="D168" s="4"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="4"/>
-      <c r="B169" s="4"/>
-      <c r="C169" s="4"/>
-      <c r="D169" s="4"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="4"/>
-      <c r="B170" s="4"/>
-      <c r="C170" s="4"/>
-      <c r="D170" s="4"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="4"/>
-      <c r="B171" s="4"/>
-      <c r="C171" s="4"/>
-      <c r="D171" s="4"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="4"/>
-      <c r="B172" s="4"/>
-      <c r="C172" s="4"/>
-      <c r="D172" s="4"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="4"/>
-      <c r="B173" s="4"/>
-      <c r="C173" s="4"/>
-      <c r="D173" s="4"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="4"/>
-      <c r="B174" s="4"/>
-      <c r="C174" s="4"/>
-      <c r="D174" s="4"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="4"/>
-      <c r="B175" s="4"/>
-      <c r="C175" s="4"/>
-      <c r="D175" s="4"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="4"/>
-      <c r="B176" s="4"/>
-      <c r="C176" s="4"/>
-      <c r="D176" s="4"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="4"/>
-      <c r="B177" s="4"/>
-      <c r="C177" s="4"/>
-      <c r="D177" s="4"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="4"/>
-      <c r="B178" s="4"/>
-      <c r="C178" s="4"/>
-      <c r="D178" s="4"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="4"/>
-      <c r="B179" s="4"/>
-      <c r="C179" s="4"/>
-      <c r="D179" s="4"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="4"/>
-      <c r="B180" s="4"/>
-      <c r="C180" s="4"/>
-      <c r="D180" s="4"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="4"/>
-      <c r="B181" s="4"/>
-      <c r="C181" s="4"/>
-      <c r="D181" s="4"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="4"/>
-      <c r="B182" s="4"/>
-      <c r="C182" s="4"/>
-      <c r="D182" s="4"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="4"/>
-      <c r="B183" s="4"/>
-      <c r="C183" s="4"/>
-      <c r="D183" s="4"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="4"/>
-      <c r="B184" s="4"/>
-      <c r="C184" s="4"/>
-      <c r="D184" s="4"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="4"/>
-      <c r="B185" s="4"/>
-      <c r="C185" s="4"/>
-      <c r="D185" s="4"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="4"/>
-      <c r="B186" s="4"/>
-      <c r="C186" s="4"/>
-      <c r="D186" s="4"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="4"/>
-      <c r="B187" s="4"/>
-      <c r="C187" s="4"/>
-      <c r="D187" s="4"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="4"/>
-      <c r="B188" s="4"/>
-      <c r="C188" s="4"/>
-      <c r="D188" s="4"/>
-    </row>
-    <row r="189">
-      <c r="A189" s="4"/>
-      <c r="B189" s="4"/>
-      <c r="C189" s="4"/>
-      <c r="D189" s="4"/>
-    </row>
-    <row r="190">
-      <c r="A190" s="4"/>
-      <c r="B190" s="4"/>
-      <c r="C190" s="4"/>
-      <c r="D190" s="4"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="4"/>
-      <c r="B191" s="4"/>
-      <c r="C191" s="4"/>
-      <c r="D191" s="4"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="4"/>
-      <c r="B192" s="4"/>
-      <c r="C192" s="4"/>
-      <c r="D192" s="4"/>
-    </row>
-    <row r="193">
-      <c r="A193" s="4"/>
-      <c r="B193" s="4"/>
-      <c r="C193" s="4"/>
-      <c r="D193" s="4"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="4"/>
-      <c r="B194" s="4"/>
-      <c r="C194" s="4"/>
-      <c r="D194" s="4"/>
-    </row>
-    <row r="195">
-      <c r="A195" s="4"/>
-      <c r="B195" s="4"/>
-      <c r="C195" s="4"/>
-      <c r="D195" s="4"/>
-    </row>
-    <row r="196">
-      <c r="A196" s="4"/>
-      <c r="B196" s="4"/>
-      <c r="C196" s="4"/>
-      <c r="D196" s="4"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="4"/>
-      <c r="B197" s="4"/>
-      <c r="C197" s="4"/>
-      <c r="D197" s="4"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="4"/>
-      <c r="B198" s="4"/>
-      <c r="C198" s="4"/>
-      <c r="D198" s="4"/>
-    </row>
-    <row r="199">
-      <c r="A199" s="4"/>
-      <c r="B199" s="4"/>
-      <c r="C199" s="4"/>
-      <c r="D199" s="4"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="4"/>
-      <c r="B200" s="4"/>
-      <c r="C200" s="4"/>
-      <c r="D200" s="4"/>
-    </row>
-    <row r="201">
-      <c r="A201" s="4"/>
-      <c r="B201" s="4"/>
-      <c r="C201" s="4"/>
-      <c r="D201" s="4"/>
-    </row>
-    <row r="202">
-      <c r="A202" s="4"/>
-      <c r="B202" s="4"/>
-      <c r="C202" s="4"/>
-      <c r="D202" s="4"/>
-    </row>
-    <row r="203">
-      <c r="A203" s="4"/>
-      <c r="B203" s="4"/>
-      <c r="C203" s="4"/>
-      <c r="D203" s="4"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="4"/>
-      <c r="B204" s="4"/>
-      <c r="C204" s="4"/>
-      <c r="D204" s="4"/>
-    </row>
-    <row r="205">
-      <c r="A205" s="4"/>
-      <c r="B205" s="4"/>
-      <c r="C205" s="4"/>
-      <c r="D205" s="4"/>
-    </row>
-    <row r="206">
-      <c r="A206" s="4"/>
-      <c r="B206" s="4"/>
-      <c r="C206" s="4"/>
-      <c r="D206" s="4"/>
-    </row>
-    <row r="207">
-      <c r="A207" s="4"/>
-      <c r="B207" s="4"/>
-      <c r="C207" s="4"/>
-      <c r="D207" s="4"/>
-    </row>
-    <row r="208">
-      <c r="A208" s="4"/>
-      <c r="B208" s="4"/>
-      <c r="C208" s="4"/>
-      <c r="D208" s="4"/>
-    </row>
-    <row r="209">
-      <c r="A209" s="4"/>
-      <c r="B209" s="4"/>
-      <c r="C209" s="4"/>
-      <c r="D209" s="4"/>
-    </row>
-    <row r="210">
-      <c r="A210" s="4"/>
-      <c r="B210" s="4"/>
-      <c r="C210" s="4"/>
-      <c r="D210" s="4"/>
-    </row>
-    <row r="211">
-      <c r="A211" s="4"/>
-      <c r="B211" s="4"/>
-      <c r="C211" s="4"/>
-      <c r="D211" s="4"/>
-    </row>
-    <row r="212">
-      <c r="A212" s="4"/>
-      <c r="B212" s="4"/>
-      <c r="C212" s="4"/>
-      <c r="D212" s="4"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="4"/>
-      <c r="B213" s="4"/>
-      <c r="C213" s="4"/>
-      <c r="D213" s="4"/>
-    </row>
-    <row r="214">
-      <c r="A214" s="4"/>
-      <c r="B214" s="4"/>
-      <c r="C214" s="4"/>
-      <c r="D214" s="4"/>
-    </row>
-    <row r="215">
-      <c r="A215" s="4"/>
-      <c r="B215" s="4"/>
-      <c r="C215" s="4"/>
-      <c r="D215" s="4"/>
-    </row>
-    <row r="216">
-      <c r="A216" s="4"/>
-      <c r="B216" s="4"/>
-      <c r="C216" s="4"/>
-      <c r="D216" s="4"/>
-    </row>
-    <row r="217">
-      <c r="A217" s="4"/>
-      <c r="B217" s="4"/>
-      <c r="C217" s="4"/>
-      <c r="D217" s="4"/>
-    </row>
-    <row r="218">
-      <c r="A218" s="4"/>
-      <c r="B218" s="4"/>
-      <c r="C218" s="4"/>
-      <c r="D218" s="4"/>
-    </row>
-    <row r="219">
-      <c r="A219" s="4"/>
-      <c r="B219" s="4"/>
-      <c r="C219" s="4"/>
-      <c r="D219" s="4"/>
-    </row>
-    <row r="220">
-      <c r="A220" s="4"/>
-      <c r="B220" s="4"/>
-      <c r="C220" s="4"/>
-      <c r="D220" s="4"/>
-    </row>
-    <row r="221">
-      <c r="A221" s="4"/>
-      <c r="B221" s="4"/>
-      <c r="C221" s="4"/>
-      <c r="D221" s="4"/>
-    </row>
-    <row r="222">
-      <c r="A222" s="4"/>
-      <c r="B222" s="4"/>
-      <c r="C222" s="4"/>
-      <c r="D222" s="4"/>
-    </row>
-    <row r="223">
-      <c r="A223" s="4"/>
-      <c r="B223" s="4"/>
-      <c r="C223" s="4"/>
-      <c r="D223" s="4"/>
-    </row>
-    <row r="224">
-      <c r="A224" s="4"/>
-      <c r="B224" s="4"/>
-      <c r="C224" s="4"/>
-      <c r="D224" s="4"/>
-    </row>
-    <row r="225">
-      <c r="A225" s="4"/>
-      <c r="B225" s="4"/>
-      <c r="C225" s="4"/>
-      <c r="D225" s="4"/>
-    </row>
-    <row r="226">
-      <c r="A226" s="4"/>
-      <c r="B226" s="4"/>
-      <c r="C226" s="4"/>
-      <c r="D226" s="4"/>
-    </row>
-    <row r="227">
-      <c r="A227" s="4"/>
-      <c r="B227" s="4"/>
-      <c r="C227" s="4"/>
-      <c r="D227" s="4"/>
-    </row>
-    <row r="228">
-      <c r="A228" s="4"/>
-      <c r="B228" s="4"/>
-      <c r="C228" s="4"/>
-      <c r="D228" s="4"/>
-    </row>
-    <row r="229">
-      <c r="A229" s="4"/>
-      <c r="B229" s="4"/>
-      <c r="C229" s="4"/>
-      <c r="D229" s="4"/>
-    </row>
-    <row r="230">
-      <c r="A230" s="4"/>
-      <c r="B230" s="4"/>
-      <c r="C230" s="4"/>
-      <c r="D230" s="4"/>
-    </row>
-    <row r="231">
-      <c r="A231" s="4"/>
-      <c r="B231" s="4"/>
-      <c r="C231" s="4"/>
-      <c r="D231" s="4"/>
-    </row>
-    <row r="232">
-      <c r="A232" s="4"/>
-      <c r="B232" s="4"/>
-      <c r="C232" s="4"/>
-      <c r="D232" s="4"/>
-    </row>
-    <row r="233">
-      <c r="A233" s="4"/>
-      <c r="B233" s="4"/>
-      <c r="C233" s="4"/>
-      <c r="D233" s="4"/>
-    </row>
-    <row r="234">
-      <c r="A234" s="4"/>
-      <c r="B234" s="4"/>
-      <c r="C234" s="4"/>
-      <c r="D234" s="4"/>
-    </row>
-    <row r="235">
-      <c r="A235" s="4"/>
-      <c r="B235" s="4"/>
-      <c r="C235" s="4"/>
-      <c r="D235" s="4"/>
-    </row>
-    <row r="236">
-      <c r="A236" s="4"/>
-      <c r="B236" s="4"/>
-      <c r="C236" s="4"/>
-      <c r="D236" s="4"/>
-    </row>
-    <row r="237">
-      <c r="A237" s="4"/>
-      <c r="B237" s="4"/>
-      <c r="C237" s="4"/>
-      <c r="D237" s="4"/>
-    </row>
-    <row r="238">
-      <c r="A238" s="4"/>
-      <c r="B238" s="4"/>
-      <c r="C238" s="4"/>
-      <c r="D238" s="4"/>
-    </row>
-    <row r="239">
-      <c r="A239" s="4"/>
-      <c r="B239" s="4"/>
-      <c r="C239" s="4"/>
-      <c r="D239" s="4"/>
-    </row>
-    <row r="240">
-      <c r="A240" s="4"/>
-      <c r="B240" s="4"/>
-      <c r="C240" s="4"/>
-      <c r="D240" s="4"/>
-    </row>
-    <row r="241">
-      <c r="A241" s="4"/>
-      <c r="B241" s="4"/>
-      <c r="C241" s="4"/>
-      <c r="D241" s="4"/>
-    </row>
-    <row r="242">
-      <c r="A242" s="4"/>
-      <c r="B242" s="4"/>
-      <c r="C242" s="4"/>
-      <c r="D242" s="4"/>
-    </row>
-    <row r="243">
-      <c r="A243" s="4"/>
-      <c r="B243" s="4"/>
-      <c r="C243" s="4"/>
-      <c r="D243" s="4"/>
-    </row>
-    <row r="244">
-      <c r="A244" s="4"/>
-      <c r="B244" s="4"/>
-      <c r="C244" s="4"/>
-      <c r="D244" s="4"/>
-    </row>
-    <row r="245">
-      <c r="A245" s="4"/>
-      <c r="B245" s="4"/>
-      <c r="C245" s="4"/>
-      <c r="D245" s="4"/>
-    </row>
-    <row r="246">
-      <c r="A246" s="4"/>
-      <c r="B246" s="4"/>
-      <c r="C246" s="4"/>
-      <c r="D246" s="4"/>
-    </row>
-    <row r="247">
-      <c r="A247" s="4"/>
-      <c r="B247" s="4"/>
-      <c r="C247" s="4"/>
-      <c r="D247" s="4"/>
-    </row>
-    <row r="248">
-      <c r="A248" s="4"/>
-      <c r="B248" s="4"/>
-      <c r="C248" s="4"/>
-      <c r="D248" s="4"/>
-    </row>
-    <row r="249">
-      <c r="A249" s="4"/>
-      <c r="B249" s="4"/>
-      <c r="C249" s="4"/>
-      <c r="D249" s="4"/>
-    </row>
-    <row r="250">
-      <c r="A250" s="4"/>
-      <c r="B250" s="4"/>
-      <c r="C250" s="4"/>
-      <c r="D250" s="4"/>
-    </row>
-    <row r="251">
-      <c r="A251" s="4"/>
-      <c r="B251" s="4"/>
-      <c r="C251" s="4"/>
-      <c r="D251" s="4"/>
-    </row>
-    <row r="252">
-      <c r="A252" s="4"/>
-      <c r="B252" s="4"/>
-      <c r="C252" s="4"/>
-      <c r="D252" s="4"/>
-    </row>
-    <row r="253">
-      <c r="A253" s="4"/>
-      <c r="B253" s="4"/>
-      <c r="C253" s="4"/>
-      <c r="D253" s="4"/>
-    </row>
-    <row r="254">
-      <c r="A254" s="4"/>
-      <c r="B254" s="4"/>
-      <c r="C254" s="4"/>
-      <c r="D254" s="4"/>
-    </row>
-    <row r="255">
-      <c r="A255" s="4"/>
-      <c r="B255" s="4"/>
-      <c r="C255" s="4"/>
-      <c r="D255" s="4"/>
-    </row>
-    <row r="256">
-      <c r="A256" s="4"/>
-      <c r="B256" s="4"/>
-      <c r="C256" s="4"/>
-      <c r="D256" s="4"/>
-    </row>
-    <row r="257">
-      <c r="A257" s="4"/>
-      <c r="B257" s="4"/>
-      <c r="C257" s="4"/>
-      <c r="D257" s="4"/>
-    </row>
-    <row r="258">
-      <c r="A258" s="4"/>
-      <c r="B258" s="4"/>
-      <c r="C258" s="4"/>
-      <c r="D258" s="4"/>
-    </row>
-    <row r="259">
-      <c r="A259" s="4"/>
-      <c r="B259" s="4"/>
-      <c r="C259" s="4"/>
-      <c r="D259" s="4"/>
-    </row>
-    <row r="260">
-      <c r="A260" s="4"/>
-      <c r="B260" s="4"/>
-      <c r="C260" s="4"/>
-      <c r="D260" s="4"/>
-    </row>
-    <row r="261">
-      <c r="A261" s="4"/>
-      <c r="B261" s="4"/>
-      <c r="C261" s="4"/>
-      <c r="D261" s="4"/>
-    </row>
-    <row r="262">
-      <c r="A262" s="4"/>
-      <c r="B262" s="4"/>
-      <c r="C262" s="4"/>
-      <c r="D262" s="4"/>
-    </row>
-    <row r="263">
-      <c r="A263" s="4"/>
-      <c r="B263" s="4"/>
-      <c r="C263" s="4"/>
-      <c r="D263" s="4"/>
-    </row>
-    <row r="264">
-      <c r="A264" s="4"/>
-      <c r="B264" s="4"/>
-      <c r="C264" s="4"/>
-      <c r="D264" s="4"/>
-    </row>
-    <row r="265">
-      <c r="A265" s="4"/>
-      <c r="B265" s="4"/>
-      <c r="C265" s="4"/>
-      <c r="D265" s="4"/>
-    </row>
-    <row r="266">
-      <c r="A266" s="4"/>
-      <c r="B266" s="4"/>
-      <c r="C266" s="4"/>
-      <c r="D266" s="4"/>
-    </row>
-    <row r="267">
-      <c r="A267" s="4"/>
-      <c r="B267" s="4"/>
-      <c r="C267" s="4"/>
-      <c r="D267" s="4"/>
-    </row>
-    <row r="268">
-      <c r="A268" s="4"/>
-      <c r="B268" s="4"/>
-      <c r="C268" s="4"/>
-      <c r="D268" s="4"/>
-    </row>
-    <row r="269">
-      <c r="A269" s="4"/>
-      <c r="B269" s="4"/>
-      <c r="C269" s="4"/>
-      <c r="D269" s="4"/>
-    </row>
-    <row r="270">
-      <c r="A270" s="4"/>
-      <c r="B270" s="4"/>
-      <c r="C270" s="4"/>
-      <c r="D270" s="4"/>
-    </row>
-    <row r="271">
-      <c r="A271" s="4"/>
-      <c r="B271" s="4"/>
-      <c r="C271" s="4"/>
-      <c r="D271" s="4"/>
-    </row>
-    <row r="272">
-      <c r="A272" s="4"/>
-      <c r="B272" s="4"/>
-      <c r="C272" s="4"/>
-      <c r="D272" s="4"/>
-    </row>
-    <row r="273">
-      <c r="A273" s="4"/>
-      <c r="B273" s="4"/>
-      <c r="C273" s="4"/>
-      <c r="D273" s="4"/>
-    </row>
-    <row r="274">
-      <c r="A274" s="4"/>
-      <c r="B274" s="4"/>
-      <c r="C274" s="4"/>
-      <c r="D274" s="4"/>
-    </row>
-    <row r="275">
-      <c r="A275" s="4"/>
-      <c r="B275" s="4"/>
-      <c r="C275" s="4"/>
-      <c r="D275" s="4"/>
-    </row>
-    <row r="276">
-      <c r="A276" s="4"/>
-      <c r="B276" s="4"/>
-      <c r="C276" s="4"/>
-      <c r="D276" s="4"/>
-    </row>
-    <row r="277">
-      <c r="A277" s="4"/>
-      <c r="B277" s="4"/>
-      <c r="C277" s="4"/>
-      <c r="D277" s="4"/>
-    </row>
-    <row r="278">
-      <c r="A278" s="4"/>
-      <c r="B278" s="4"/>
-      <c r="C278" s="4"/>
-      <c r="D278" s="4"/>
-    </row>
-    <row r="279">
-      <c r="A279" s="4"/>
-      <c r="B279" s="4"/>
-      <c r="C279" s="4"/>
-      <c r="D279" s="4"/>
-    </row>
-    <row r="280">
-      <c r="A280" s="4"/>
-      <c r="B280" s="4"/>
-      <c r="C280" s="4"/>
-      <c r="D280" s="4"/>
-    </row>
-    <row r="281">
-      <c r="A281" s="4"/>
-      <c r="B281" s="4"/>
-      <c r="C281" s="4"/>
-      <c r="D281" s="4"/>
-    </row>
-    <row r="282">
-      <c r="A282" s="4"/>
-      <c r="B282" s="4"/>
-      <c r="C282" s="4"/>
-      <c r="D282" s="4"/>
-    </row>
-    <row r="283">
-      <c r="A283" s="4"/>
-      <c r="B283" s="4"/>
-      <c r="C283" s="4"/>
-      <c r="D283" s="4"/>
-    </row>
-    <row r="284">
-      <c r="A284" s="4"/>
-      <c r="B284" s="4"/>
-      <c r="C284" s="4"/>
-      <c r="D284" s="4"/>
-    </row>
-    <row r="285">
-      <c r="A285" s="4"/>
-      <c r="B285" s="4"/>
-      <c r="C285" s="4"/>
-      <c r="D285" s="4"/>
-    </row>
-    <row r="286">
-      <c r="A286" s="4"/>
-      <c r="B286" s="4"/>
-      <c r="C286" s="4"/>
-      <c r="D286" s="4"/>
-    </row>
-    <row r="287">
-      <c r="A287" s="4"/>
-      <c r="B287" s="4"/>
-      <c r="C287" s="4"/>
-      <c r="D287" s="4"/>
-    </row>
-    <row r="288">
-      <c r="A288" s="4"/>
-      <c r="B288" s="4"/>
-      <c r="C288" s="4"/>
-      <c r="D288" s="4"/>
-    </row>
-    <row r="289">
-      <c r="A289" s="4"/>
-      <c r="B289" s="4"/>
-      <c r="C289" s="4"/>
-      <c r="D289" s="4"/>
-    </row>
-    <row r="290">
-      <c r="A290" s="4"/>
-      <c r="B290" s="4"/>
-      <c r="C290" s="4"/>
-      <c r="D290" s="4"/>
-    </row>
-    <row r="291">
-      <c r="A291" s="4"/>
-      <c r="B291" s="4"/>
-      <c r="C291" s="4"/>
-      <c r="D291" s="4"/>
-    </row>
-    <row r="292">
-      <c r="A292" s="4"/>
-      <c r="B292" s="4"/>
-      <c r="C292" s="4"/>
-      <c r="D292" s="4"/>
-    </row>
-    <row r="293">
-      <c r="A293" s="4"/>
-      <c r="B293" s="4"/>
-      <c r="C293" s="4"/>
-      <c r="D293" s="4"/>
-    </row>
-    <row r="294">
-      <c r="A294" s="4"/>
-      <c r="B294" s="4"/>
-      <c r="C294" s="4"/>
-      <c r="D294" s="4"/>
-    </row>
-    <row r="295">
-      <c r="A295" s="4"/>
-      <c r="B295" s="4"/>
-      <c r="C295" s="4"/>
-      <c r="D295" s="4"/>
-    </row>
-    <row r="296">
-      <c r="A296" s="4"/>
-      <c r="B296" s="4"/>
-      <c r="C296" s="4"/>
-      <c r="D296" s="4"/>
-    </row>
-    <row r="297">
-      <c r="A297" s="4"/>
-      <c r="B297" s="4"/>
-      <c r="C297" s="4"/>
-      <c r="D297" s="4"/>
-    </row>
-    <row r="298">
-      <c r="A298" s="4"/>
-      <c r="B298" s="4"/>
-      <c r="C298" s="4"/>
-      <c r="D298" s="4"/>
-    </row>
-    <row r="299">
-      <c r="A299" s="4"/>
-      <c r="B299" s="4"/>
-      <c r="C299" s="4"/>
-      <c r="D299" s="4"/>
-    </row>
-    <row r="300">
-      <c r="A300" s="4"/>
-      <c r="B300" s="4"/>
-      <c r="C300" s="4"/>
-      <c r="D300" s="4"/>
-    </row>
-  </sheetData>
-  <dataValidations count="3">
-    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" errorTitle="Valore non valido" error="Spessore in mm (numero, es. 1.5)." sqref="A2:A300">
-      <formula1>0.1</formula1>
-      <formula2>60</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Valore non valido" error="Peso in kg/m² (&gt; 0)." sqref="C2:C300">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Valore non valido" error="Consumo in m³/h (&gt; 0)." sqref="D2:D300">
-      <formula1>0</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D300"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="14.00390625" customWidth="1"/>
-    <col min="2" max="2" width="12.00390625" customWidth="1"/>
-    <col min="3" max="3" width="13.57421875" customWidth="1"/>
-    <col min="4" max="4" width="18.00390625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="4">
-        <v>2.16</v>
-      </c>
-      <c r="D2" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="4">
-        <v>2.7</v>
-      </c>
-      <c r="D3" s="4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="4">
-        <v>3.24</v>
-      </c>
-      <c r="D4" s="4">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="4">
-        <v>4.05</v>
-      </c>
-      <c r="D5" s="4">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4">
-        <v>2</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="4">
-        <v>5.4</v>
-      </c>
-      <c r="D6" s="4">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4">
-        <v>2.5</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="4">
-        <v>6.75</v>
-      </c>
-      <c r="D7" s="4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4">
-        <v>3</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" s="4">
-        <v>8.1</v>
-      </c>
-      <c r="D8" s="4">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4">
-        <v>4</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="4">
-        <v>10.8</v>
-      </c>
-      <c r="D9" s="4">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4">
-        <v>5</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" s="4">
-        <v>13.5</v>
-      </c>
-      <c r="D10" s="4">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4">
-        <v>6</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4">
-        <v>8</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4">
-        <v>72</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="4"/>

--- a/cosatcal/CosatCal_dati.xlsx
+++ b/cosatcal/CosatCal_dati.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="4"/>
+    <workbookView activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="LEGGIMI" sheetId="1" r:id="rId1"/>
@@ -2430,7 +2430,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B298"/>
+  <dimension ref="A1:B297"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.00390625" customWidth="1"/>
@@ -3649,13 +3649,9 @@
       <c r="A297" s="4"/>
       <c r="B297" s="4"/>
     </row>
-    <row r="298">
-      <c r="A298" s="4"/>
-      <c r="B298" s="4"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Valore non valido" error="Inserire un prezzo &gt;= 0 (€/kg)." sqref="B2:B298">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Valore non valido" error="Inserire un prezzo &gt;= 0 (€/kg)." sqref="B2:B297">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/cosatcal/CosatCal_dati.xlsx
+++ b/cosatcal/CosatCal_dati.xlsx
@@ -2430,7 +2430,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B297"/>
+  <dimension ref="A1:B290"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.00390625" customWidth="1"/>
@@ -3621,37 +3621,9 @@
       <c r="A290" s="4"/>
       <c r="B290" s="4"/>
     </row>
-    <row r="291">
-      <c r="A291" s="4"/>
-      <c r="B291" s="4"/>
-    </row>
-    <row r="292">
-      <c r="A292" s="4"/>
-      <c r="B292" s="4"/>
-    </row>
-    <row r="293">
-      <c r="A293" s="4"/>
-      <c r="B293" s="4"/>
-    </row>
-    <row r="294">
-      <c r="A294" s="4"/>
-      <c r="B294" s="4"/>
-    </row>
-    <row r="295">
-      <c r="A295" s="4"/>
-      <c r="B295" s="4"/>
-    </row>
-    <row r="296">
-      <c r="A296" s="4"/>
-      <c r="B296" s="4"/>
-    </row>
-    <row r="297">
-      <c r="A297" s="4"/>
-      <c r="B297" s="4"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Valore non valido" error="Inserire un prezzo &gt;= 0 (€/kg)." sqref="B2:B297">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Valore non valido" error="Inserire un prezzo &gt;= 0 (€/kg)." sqref="B2:B6 B7:B290">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/cosatcal/CosatCal_dati.xlsx
+++ b/cosatcal/CosatCal_dati.xlsx
@@ -1,9 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="gridcraft"/>
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="2"/>
+    <workbookView activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="LEGGIMI" sheetId="1" r:id="rId1"/>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="50">
   <si>
     <t>Base dati CosatCal</t>
   </si>
@@ -157,7 +158,7 @@
     <t>spessore_mm</t>
   </si>
   <si>
-    <t>codice</t>
+    <t>gas</t>
   </si>
   <si>
     <t>peso_kgm2</t>
@@ -166,26 +167,17 @@
     <t>consumo_gas_m3h</t>
   </si>
   <si>
-    <t>DC01</t>
+    <t>Ossigeno</t>
   </si>
   <si>
-    <t>DD11</t>
-  </si>
-  <si>
-    <t>14301</t>
-  </si>
-  <si>
-    <t>AW5754</t>
-  </si>
-  <si>
-    <t>DX51D</t>
+    <t>Azoto</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -213,6 +205,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -236,7 +235,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -246,6 +245,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -284,7 +284,7 @@
   <autoFilter ref="A1:D14"/>
   <tableColumns count="4">
     <tableColumn id="1" name="spessore_mm"/>
-    <tableColumn id="2" name="codice"/>
+    <tableColumn id="2" name="gas"/>
     <tableColumn id="3" name="peso_kgm2"/>
     <tableColumn id="4" name="consumo_gas_m3h"/>
   </tableColumns>
@@ -297,7 +297,7 @@
   <autoFilter ref="A1:D11"/>
   <tableColumns count="4">
     <tableColumn id="1" name="spessore_mm"/>
-    <tableColumn id="2" name="codice"/>
+    <tableColumn id="2" name="gas"/>
     <tableColumn id="3" name="peso_kgm2"/>
     <tableColumn id="4" name="consumo_gas_m3h"/>
   </tableColumns>
@@ -310,7 +310,7 @@
   <autoFilter ref="A1:D9"/>
   <tableColumns count="4">
     <tableColumn id="1" name="spessore_mm"/>
-    <tableColumn id="2" name="codice"/>
+    <tableColumn id="2" name="gas"/>
     <tableColumn id="3" name="peso_kgm2"/>
     <tableColumn id="4" name="consumo_gas_m3h"/>
   </tableColumns>
@@ -323,7 +323,7 @@
   <autoFilter ref="A1:D12"/>
   <tableColumns count="4">
     <tableColumn id="1" name="spessore_mm"/>
-    <tableColumn id="2" name="codice"/>
+    <tableColumn id="2" name="gas"/>
     <tableColumn id="3" name="peso_kgm2"/>
     <tableColumn id="4" name="consumo_gas_m3h"/>
   </tableColumns>
@@ -336,7 +336,7 @@
   <autoFilter ref="A1:D8"/>
   <tableColumns count="4">
     <tableColumn id="1" name="spessore_mm"/>
-    <tableColumn id="2" name="codice"/>
+    <tableColumn id="2" name="gas"/>
     <tableColumn id="3" name="peso_kgm2"/>
     <tableColumn id="4" name="consumo_gas_m3h"/>
   </tableColumns>
@@ -2430,7 +2430,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B290"/>
+  <dimension ref="A1:B289"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.00390625" customWidth="1"/>
@@ -3617,13 +3617,9 @@
       <c r="A289" s="4"/>
       <c r="B289" s="4"/>
     </row>
-    <row r="290">
-      <c r="A290" s="4"/>
-      <c r="B290" s="4"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Valore non valido" error="Inserire un prezzo &gt;= 0 (€/kg)." sqref="B2:B6 B7:B290">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Valore non valido" error="Inserire un prezzo &gt;= 0 (€/kg)." sqref="B2:B6 B7:B289">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -3637,7 +3633,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D300"/>
+  <dimension ref="A1:D288"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.00390625" customWidth="1"/>
@@ -3762,7 +3758,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C9" s="4">
         <v>31.4</v>
@@ -3776,7 +3772,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C10" s="4">
         <v>39.25</v>
@@ -3790,7 +3786,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C11" s="4">
         <v>47.1</v>
@@ -3804,7 +3800,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C12" s="4">
         <v>62.8</v>
@@ -3818,7 +3814,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C13" s="4">
         <v>78.5</v>
@@ -3832,7 +3828,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" s="4">
         <v>94.2</v>
@@ -5485,88 +5481,16 @@
       <c r="C288" s="4"/>
       <c r="D288" s="4"/>
     </row>
-    <row r="289">
-      <c r="A289" s="4"/>
-      <c r="B289" s="4"/>
-      <c r="C289" s="4"/>
-      <c r="D289" s="4"/>
-    </row>
-    <row r="290">
-      <c r="A290" s="4"/>
-      <c r="B290" s="4"/>
-      <c r="C290" s="4"/>
-      <c r="D290" s="4"/>
-    </row>
-    <row r="291">
-      <c r="A291" s="4"/>
-      <c r="B291" s="4"/>
-      <c r="C291" s="4"/>
-      <c r="D291" s="4"/>
-    </row>
-    <row r="292">
-      <c r="A292" s="4"/>
-      <c r="B292" s="4"/>
-      <c r="C292" s="4"/>
-      <c r="D292" s="4"/>
-    </row>
-    <row r="293">
-      <c r="A293" s="4"/>
-      <c r="B293" s="4"/>
-      <c r="C293" s="4"/>
-      <c r="D293" s="4"/>
-    </row>
-    <row r="294">
-      <c r="A294" s="4"/>
-      <c r="B294" s="4"/>
-      <c r="C294" s="4"/>
-      <c r="D294" s="4"/>
-    </row>
-    <row r="295">
-      <c r="A295" s="4"/>
-      <c r="B295" s="4"/>
-      <c r="C295" s="4"/>
-      <c r="D295" s="4"/>
-    </row>
-    <row r="296">
-      <c r="A296" s="4"/>
-      <c r="B296" s="4"/>
-      <c r="C296" s="4"/>
-      <c r="D296" s="4"/>
-    </row>
-    <row r="297">
-      <c r="A297" s="4"/>
-      <c r="B297" s="4"/>
-      <c r="C297" s="4"/>
-      <c r="D297" s="4"/>
-    </row>
-    <row r="298">
-      <c r="A298" s="4"/>
-      <c r="B298" s="4"/>
-      <c r="C298" s="4"/>
-      <c r="D298" s="4"/>
-    </row>
-    <row r="299">
-      <c r="A299" s="4"/>
-      <c r="B299" s="4"/>
-      <c r="C299" s="4"/>
-      <c r="D299" s="4"/>
-    </row>
-    <row r="300">
-      <c r="A300" s="4"/>
-      <c r="B300" s="4"/>
-      <c r="C300" s="4"/>
-      <c r="D300" s="4"/>
-    </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" errorTitle="Valore non valido" error="Spessore in mm (numero, es. 1.5)." sqref="A2:A300">
+    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" errorTitle="Valore non valido" error="Spessore in mm (numero, es. 1.5)." sqref="A2:A14 A15:A288">
       <formula1>0.1</formula1>
       <formula2>60</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Valore non valido" error="Peso in kg/m² (&gt; 0)." sqref="C2:C300">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Valore non valido" error="Peso in kg/m² (&gt; 0)." sqref="C2:C14 C15:C288">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Valore non valido" error="Consumo in m³/h (&gt; 0)." sqref="D2:D300">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Valore non valido" error="Consumo in m³/h (&gt; 0)." sqref="D2:D14 D15:D288">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -5608,7 +5532,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2" s="4">
         <v>6.28</v>
@@ -5622,7 +5546,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C3" s="4">
         <v>7.85</v>
@@ -5636,7 +5560,7 @@
         <v>1.2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C4" s="4">
         <v>9.42</v>
@@ -5650,7 +5574,7 @@
         <v>1.5</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C5" s="4">
         <v>11.8</v>
@@ -5664,7 +5588,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C6" s="4">
         <v>15.7</v>
@@ -5678,7 +5602,7 @@
         <v>2.5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C7" s="4">
         <v>19.6</v>
@@ -5692,7 +5616,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C8" s="4">
         <v>23.6</v>
@@ -5706,7 +5630,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C9" s="4">
         <v>31.4</v>
@@ -5720,7 +5644,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C10" s="4">
         <v>39.25</v>
@@ -5734,7 +5658,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" s="4">
         <v>47.1</v>
@@ -7527,7 +7451,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2" s="4">
         <v>6.28</v>
@@ -7541,7 +7465,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C3" s="4">
         <v>7.85</v>
@@ -7555,7 +7479,7 @@
         <v>1.2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C4" s="4">
         <v>9.42</v>
@@ -7569,7 +7493,7 @@
         <v>1.5</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C5" s="4">
         <v>11.8</v>
@@ -7583,7 +7507,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C6" s="4">
         <v>15.7</v>
@@ -7597,7 +7521,7 @@
         <v>2.5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C7" s="4">
         <v>19.6</v>
@@ -7611,7 +7535,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C8" s="4">
         <v>23.6</v>
@@ -7625,7 +7549,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C9" s="4">
         <v>31.4</v>
@@ -9431,7 +9355,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C2" s="4">
         <v>2.16</v>
@@ -9445,7 +9369,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C3" s="4">
         <v>2.7</v>
@@ -9459,7 +9383,7 @@
         <v>1.2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C4" s="4">
         <v>3.24</v>
@@ -9473,7 +9397,7 @@
         <v>1.5</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C5" s="4">
         <v>4.05</v>
@@ -9487,7 +9411,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C6" s="4">
         <v>5.4</v>
@@ -9501,7 +9425,7 @@
         <v>2.5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C7" s="4">
         <v>6.75</v>
@@ -9515,7 +9439,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C8" s="4">
         <v>8.1</v>
@@ -9529,7 +9453,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C9" s="4">
         <v>10.8</v>
@@ -9543,7 +9467,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C10" s="4">
         <v>13.5</v>
@@ -9557,7 +9481,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4">
@@ -9569,7 +9493,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4">
@@ -11354,7 +11278,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C2" s="4">
         <v>6.28</v>
@@ -11368,7 +11292,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C3" s="4">
         <v>7.85</v>
@@ -11382,7 +11306,7 @@
         <v>1.2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C4" s="4">
         <v>9.42</v>
@@ -11396,7 +11320,7 @@
         <v>1.5</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C5" s="4">
         <v>11.8</v>
@@ -11410,7 +11334,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C6" s="4">
         <v>15.7</v>
@@ -11424,7 +11348,7 @@
         <v>2.5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C7" s="4">
         <v>19.6</v>
@@ -11438,7 +11362,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C8" s="4">
         <v>23.6</v>
